--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/59.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/59.xlsx
@@ -426,13 +426,13 @@
         <v>-8.100955799817203</v>
       </c>
       <c r="E2">
-        <v>-16.84428568193046</v>
+        <v>-16.856068342459</v>
       </c>
       <c r="F2">
-        <v>-1.488081834738748</v>
+        <v>-1.863857453140299</v>
       </c>
       <c r="G2">
-        <v>-5.899696119586238</v>
+        <v>-5.266449576033346</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.074214302062571</v>
       </c>
       <c r="E3">
-        <v>-16.53546119423886</v>
+        <v>-17.78342643954599</v>
       </c>
       <c r="F3">
-        <v>-1.202769735294723</v>
+        <v>-1.863479717604622</v>
       </c>
       <c r="G3">
-        <v>-5.390533044959779</v>
+        <v>-4.919210102436915</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.114162923200103</v>
       </c>
       <c r="E4">
-        <v>-17.93554195752916</v>
+        <v>-16.99518430899546</v>
       </c>
       <c r="F4">
-        <v>-1.310518796846466</v>
+        <v>-1.988215281118172</v>
       </c>
       <c r="G4">
-        <v>-4.338468243355902</v>
+        <v>-3.982908326747593</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.351285840147757</v>
       </c>
       <c r="E5">
-        <v>-16.91567523139294</v>
+        <v>-17.76274344714834</v>
       </c>
       <c r="F5">
-        <v>-1.369517608376055</v>
+        <v>-1.909563452957165</v>
       </c>
       <c r="G5">
-        <v>-3.841468627779439</v>
+        <v>-3.544621746280677</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.769744352601686</v>
       </c>
       <c r="E6">
-        <v>-17.66198238719668</v>
+        <v>-18.05138332780128</v>
       </c>
       <c r="F6">
-        <v>-1.421485237390682</v>
+        <v>-2.032125380405768</v>
       </c>
       <c r="G6">
-        <v>-2.667296690904604</v>
+        <v>-2.18138751835119</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.380462733680998</v>
       </c>
       <c r="E7">
-        <v>-19.65969364728451</v>
+        <v>-18.75627466027382</v>
       </c>
       <c r="F7">
-        <v>-1.767124021310984</v>
+        <v>-2.330250666836296</v>
       </c>
       <c r="G7">
-        <v>-2.501289885334074</v>
+        <v>-2.008373474298113</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.162308400103658</v>
       </c>
       <c r="E8">
-        <v>-18.61197548600398</v>
+        <v>-18.94634222334328</v>
       </c>
       <c r="F8">
-        <v>-1.509535722103852</v>
+        <v>-2.253196759395289</v>
       </c>
       <c r="G8">
-        <v>-1.741578873787655</v>
+        <v>-1.26063794819113</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.096219838450987</v>
       </c>
       <c r="E9">
-        <v>-18.65333731758795</v>
+        <v>-19.51819789065892</v>
       </c>
       <c r="F9">
-        <v>-1.920381102870323</v>
+        <v>-2.290452583336197</v>
       </c>
       <c r="G9">
-        <v>-1.747844660806327</v>
+        <v>-1.012523225230088</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.142293674504232</v>
       </c>
       <c r="E10">
-        <v>-19.76146809079943</v>
+        <v>-19.06169351467907</v>
       </c>
       <c r="F10">
-        <v>-2.089878327361547</v>
+        <v>-2.063238031687515</v>
       </c>
       <c r="G10">
-        <v>-1.325295648734641</v>
+        <v>-0.6988109336727329</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.26798626960705</v>
       </c>
       <c r="E11">
-        <v>-19.41850835922906</v>
+        <v>-19.49229015841464</v>
       </c>
       <c r="F11">
-        <v>-1.66657098738736</v>
+        <v>-1.860402332703222</v>
       </c>
       <c r="G11">
-        <v>-0.6369075686728458</v>
+        <v>-0.5085711968074901</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.430249638220468</v>
       </c>
       <c r="E12">
-        <v>-20.44895331460962</v>
+        <v>-19.79637583198461</v>
       </c>
       <c r="F12">
-        <v>-1.311972581638379</v>
+        <v>-1.502706661235173</v>
       </c>
       <c r="G12">
-        <v>-1.117182754398637</v>
+        <v>0.003317495172091909</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.591590202630691</v>
       </c>
       <c r="E13">
-        <v>-20.02596120080981</v>
+        <v>-20.3514940576612</v>
       </c>
       <c r="F13">
-        <v>-1.956809387775834</v>
+        <v>-1.422219999276965</v>
       </c>
       <c r="G13">
-        <v>-1.156759031655323</v>
+        <v>0.1619306720605885</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.726839271133595</v>
       </c>
       <c r="E14">
-        <v>-20.98371665158322</v>
+        <v>-20.91833264569645</v>
       </c>
       <c r="F14">
-        <v>-0.6415375660196129</v>
+        <v>-1.030939828197216</v>
       </c>
       <c r="G14">
-        <v>-1.296538297063529</v>
+        <v>0.1367761479252119</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.814467451507046</v>
       </c>
       <c r="E15">
-        <v>-22.71645718235831</v>
+        <v>-21.52461428168359</v>
       </c>
       <c r="F15">
-        <v>0.03758453855231142</v>
+        <v>-0.9616858282209686</v>
       </c>
       <c r="G15">
-        <v>-0.1259639662352469</v>
+        <v>0.2012850360270301</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.849591308020133</v>
       </c>
       <c r="E16">
-        <v>-22.59552812821328</v>
+        <v>-21.54903516427358</v>
       </c>
       <c r="F16">
-        <v>-0.3526709420501749</v>
+        <v>-0.5019005012971031</v>
       </c>
       <c r="G16">
-        <v>0.1876569492614188</v>
+        <v>0.05493974797217491</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.835009350910205</v>
       </c>
       <c r="E17">
-        <v>-23.10073306018807</v>
+        <v>-22.57389405042225</v>
       </c>
       <c r="F17">
-        <v>0.2641421948505734</v>
+        <v>-0.4485950589269548</v>
       </c>
       <c r="G17">
-        <v>-0.2198698384330007</v>
+        <v>0.3181184672239408</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.78397758405645</v>
       </c>
       <c r="E18">
-        <v>-23.29678955398793</v>
+        <v>-22.14736340057368</v>
       </c>
       <c r="F18">
-        <v>0.1294579388294018</v>
+        <v>0.1163216885558072</v>
       </c>
       <c r="G18">
-        <v>-0.7272602174820944</v>
+        <v>-0.1551781982098046</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.715178496773516</v>
       </c>
       <c r="E19">
-        <v>-23.27474846148706</v>
+        <v>-23.51372839432902</v>
       </c>
       <c r="F19">
-        <v>0.559938940511832</v>
+        <v>0.584794932800234</v>
       </c>
       <c r="G19">
-        <v>-0.2022890843564438</v>
+        <v>-0.05792796219083466</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.643690106711728</v>
       </c>
       <c r="E20">
-        <v>-23.32405538633543</v>
+        <v>-24.24575265638668</v>
       </c>
       <c r="F20">
-        <v>0.8737957522889256</v>
+        <v>0.8884694524621159</v>
       </c>
       <c r="G20">
-        <v>0.4599106167118944</v>
+        <v>0.121197834950039</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.58436249693256</v>
       </c>
       <c r="E21">
-        <v>-25.27275044636763</v>
+        <v>-25.11620345190087</v>
       </c>
       <c r="F21">
-        <v>1.216209701910129</v>
+        <v>1.285322051060497</v>
       </c>
       <c r="G21">
-        <v>0.8736248690872523</v>
+        <v>-0.3136164552106965</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.548168542728086</v>
       </c>
       <c r="E22">
-        <v>-25.80155807830142</v>
+        <v>-24.67055972353544</v>
       </c>
       <c r="F22">
-        <v>1.848736140074581</v>
+        <v>1.494055725952723</v>
       </c>
       <c r="G22">
-        <v>-0.4975434116546275</v>
+        <v>-0.4819207160214056</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.53901319240687</v>
       </c>
       <c r="E23">
-        <v>-25.79628765313021</v>
+        <v>-26.39821672364894</v>
       </c>
       <c r="F23">
-        <v>1.667638458474553</v>
+        <v>1.676331345999531</v>
       </c>
       <c r="G23">
-        <v>-0.576716852124729</v>
+        <v>-0.7083140439843852</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.559221676872828</v>
       </c>
       <c r="E24">
-        <v>-26.70425025333026</v>
+        <v>-26.14352519236516</v>
       </c>
       <c r="F24">
-        <v>1.786741123649066</v>
+        <v>1.748634566385483</v>
       </c>
       <c r="G24">
-        <v>-0.654381282221167</v>
+        <v>-0.4279957864919607</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.603023845225413</v>
       </c>
       <c r="E25">
-        <v>-25.9201364148366</v>
+        <v>-26.60897558553869</v>
       </c>
       <c r="F25">
-        <v>2.403371191353796</v>
+        <v>2.221446799085774</v>
       </c>
       <c r="G25">
-        <v>-1.225442500358332</v>
+        <v>-1.063962725908793</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.664167566689773</v>
       </c>
       <c r="E26">
-        <v>-26.88883973066226</v>
+        <v>-26.33219312321814</v>
       </c>
       <c r="F26">
-        <v>2.195875097361353</v>
+        <v>2.515951291598665</v>
       </c>
       <c r="G26">
-        <v>-1.284030219727505</v>
+        <v>-1.285852519452102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.736164560468125</v>
       </c>
       <c r="E27">
-        <v>-26.81179766058669</v>
+        <v>-27.76257571633439</v>
       </c>
       <c r="F27">
-        <v>1.694590220292038</v>
+        <v>2.460652797257382</v>
       </c>
       <c r="G27">
-        <v>-1.070220680693691</v>
+        <v>-1.027005025476993</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.808481001207149</v>
       </c>
       <c r="E28">
-        <v>-26.24479294409845</v>
+        <v>-26.71190046859059</v>
       </c>
       <c r="F28">
-        <v>2.653889374778033</v>
+        <v>2.41848392625047</v>
       </c>
       <c r="G28">
-        <v>-1.331838174679971</v>
+        <v>-1.007876099857906</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.873978772305055</v>
       </c>
       <c r="E29">
-        <v>-26.46118771375599</v>
+        <v>-26.52008855676471</v>
       </c>
       <c r="F29">
-        <v>2.497607923831073</v>
+        <v>2.444652052504906</v>
       </c>
       <c r="G29">
-        <v>-0.5238101129858183</v>
+        <v>-1.251181831282117</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.92838006899418</v>
       </c>
       <c r="E30">
-        <v>-26.47905898208673</v>
+        <v>-26.71858713882357</v>
       </c>
       <c r="F30">
-        <v>2.615603890155446</v>
+        <v>2.403871525265087</v>
       </c>
       <c r="G30">
-        <v>-1.524683434647145</v>
+        <v>-0.9831575700692453</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.967232877414285</v>
       </c>
       <c r="E31">
-        <v>-26.15173193794302</v>
+        <v>-26.66489026960486</v>
       </c>
       <c r="F31">
-        <v>1.933751486623895</v>
+        <v>2.361987612644738</v>
       </c>
       <c r="G31">
-        <v>-0.1585617231998874</v>
+        <v>-0.5965950614414656</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.990759130902309</v>
       </c>
       <c r="E32">
-        <v>-25.83404865049556</v>
+        <v>-26.40143130921436</v>
       </c>
       <c r="F32">
-        <v>1.810818450578837</v>
+        <v>2.153885153713446</v>
       </c>
       <c r="G32">
-        <v>-0.4658385293401477</v>
+        <v>-0.3405306212004834</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.997108633231947</v>
       </c>
       <c r="E33">
-        <v>-25.95652269925343</v>
+        <v>-25.44869293772134</v>
       </c>
       <c r="F33">
-        <v>2.024944797263287</v>
+        <v>1.910800739361932</v>
       </c>
       <c r="G33">
-        <v>-0.4416055980454343</v>
+        <v>-0.4048097637782836</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.986317040440563</v>
       </c>
       <c r="E34">
-        <v>-25.29325485067831</v>
+        <v>-25.46058358174432</v>
       </c>
       <c r="F34">
-        <v>1.219499977234049</v>
+        <v>1.935222667131266</v>
       </c>
       <c r="G34">
-        <v>-0.02535370192751419</v>
+        <v>-0.2953255786053569</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.96020997192742</v>
       </c>
       <c r="E35">
-        <v>-25.72610668816326</v>
+        <v>-25.65650301957046</v>
       </c>
       <c r="F35">
-        <v>1.816368512177593</v>
+        <v>1.572520343080697</v>
       </c>
       <c r="G35">
-        <v>-0.7933355523385806</v>
+        <v>-0.3488510642123615</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.916098282765088</v>
       </c>
       <c r="E36">
-        <v>-24.99323101778402</v>
+        <v>-25.05947473841503</v>
       </c>
       <c r="F36">
-        <v>2.055297835636666</v>
+        <v>1.863129852065625</v>
       </c>
       <c r="G36">
-        <v>-0.6058031576143221</v>
+        <v>-0.04365502151121833</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.850598052010986</v>
       </c>
       <c r="E37">
-        <v>-24.36303519098851</v>
+        <v>-24.70440839583279</v>
       </c>
       <c r="F37">
-        <v>0.6556932420710381</v>
+        <v>1.471495968104881</v>
       </c>
       <c r="G37">
-        <v>0.3448394381139853</v>
+        <v>0.4289184676707886</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.761745927521235</v>
       </c>
       <c r="E38">
-        <v>-24.87210676270672</v>
+        <v>-24.02434911387139</v>
       </c>
       <c r="F38">
-        <v>1.323208262594936</v>
+        <v>1.380501465642161</v>
       </c>
       <c r="G38">
-        <v>0.8445228991301126</v>
+        <v>0.2641674302485847</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.643296681199455</v>
       </c>
       <c r="E39">
-        <v>-23.79096355668398</v>
+        <v>-23.47881649993251</v>
       </c>
       <c r="F39">
-        <v>1.859274630172997</v>
+        <v>1.198785821959644</v>
       </c>
       <c r="G39">
-        <v>0.7945532476562043</v>
+        <v>1.28257712332842</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.49187386711533</v>
       </c>
       <c r="E40">
-        <v>-22.59740953294343</v>
+        <v>-23.02549348382748</v>
       </c>
       <c r="F40">
-        <v>1.022893601118809</v>
+        <v>1.200092985721262</v>
       </c>
       <c r="G40">
-        <v>0.3219849799633795</v>
+        <v>1.272677179838918</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.304031728230365</v>
       </c>
       <c r="E41">
-        <v>-23.04778792221916</v>
+        <v>-22.51546667350456</v>
       </c>
       <c r="F41">
-        <v>1.443329819674892</v>
+        <v>1.169965263281444</v>
       </c>
       <c r="G41">
-        <v>1.133279083141015</v>
+        <v>1.332309197044537</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.075544622591751</v>
       </c>
       <c r="E42">
-        <v>-21.20216726084655</v>
+        <v>-22.87037519405646</v>
       </c>
       <c r="F42">
-        <v>0.9389584456627459</v>
+        <v>0.8427087803966657</v>
       </c>
       <c r="G42">
-        <v>1.368577660904282</v>
+        <v>1.646702892940172</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.810014956135729</v>
       </c>
       <c r="E43">
-        <v>-20.8310902886071</v>
+        <v>-21.44007566516671</v>
       </c>
       <c r="F43">
-        <v>0.07412548142460321</v>
+        <v>0.5643135487660162</v>
       </c>
       <c r="G43">
-        <v>0.7338873755925048</v>
+        <v>2.133476221953244</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.510973358727196</v>
       </c>
       <c r="E44">
-        <v>-22.87282143552678</v>
+        <v>-21.15129457532873</v>
       </c>
       <c r="F44">
-        <v>1.198939898296565</v>
+        <v>0.7596566645919872</v>
       </c>
       <c r="G44">
-        <v>1.654790979683441</v>
+        <v>1.757223543715771</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.184926134056438</v>
       </c>
       <c r="E45">
-        <v>-21.64452995226537</v>
+        <v>-21.71080689858698</v>
       </c>
       <c r="F45">
-        <v>0.964520206978333</v>
+        <v>0.4382550825101959</v>
       </c>
       <c r="G45">
-        <v>1.947416287178374</v>
+        <v>2.19952806010841</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.845924935374356</v>
       </c>
       <c r="E46">
-        <v>-21.10743666373854</v>
+        <v>-21.50015186698035</v>
       </c>
       <c r="F46">
-        <v>0.8791287816281488</v>
+        <v>0.7678906365758144</v>
       </c>
       <c r="G46">
-        <v>1.230521486926212</v>
+        <v>1.85834290321877</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.504770077717574</v>
       </c>
       <c r="E47">
-        <v>-19.20829772123419</v>
+        <v>-20.97214580483225</v>
       </c>
       <c r="F47">
-        <v>0.4054774127488223</v>
+        <v>0.395814506995166</v>
       </c>
       <c r="G47">
-        <v>2.142741754507105</v>
+        <v>1.538740771863864</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.176763718396862</v>
       </c>
       <c r="E48">
-        <v>-21.08787919160992</v>
+        <v>-19.86680183641973</v>
       </c>
       <c r="F48">
-        <v>0.6584806983814585</v>
+        <v>0.39384796278092</v>
       </c>
       <c r="G48">
-        <v>1.979638096921894</v>
+        <v>1.625260847613359</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.875890609814167</v>
       </c>
       <c r="E49">
-        <v>-20.67826041827605</v>
+        <v>-19.41755727383568</v>
       </c>
       <c r="F49">
-        <v>0.9370846785976134</v>
+        <v>0.4272767293208941</v>
       </c>
       <c r="G49">
-        <v>0.8728050952856428</v>
+        <v>1.432723655507936</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.61205422799062</v>
       </c>
       <c r="E50">
-        <v>-20.86923338141432</v>
+        <v>-18.99490987657583</v>
       </c>
       <c r="F50">
-        <v>0.8113517607310932</v>
+        <v>0.283173935929892</v>
       </c>
       <c r="G50">
-        <v>0.9532969617742565</v>
+        <v>2.055292253683175</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.397533969388567</v>
       </c>
       <c r="E51">
-        <v>-18.38950872138954</v>
+        <v>-19.39427021793736</v>
       </c>
       <c r="F51">
-        <v>0.9057293156668464</v>
+        <v>0.4044361549235033</v>
       </c>
       <c r="G51">
-        <v>1.392191845730902</v>
+        <v>1.936453770640289</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.237797755603698</v>
       </c>
       <c r="E52">
-        <v>-18.44898686077241</v>
+        <v>-18.05706076768232</v>
       </c>
       <c r="F52">
-        <v>1.13807808847808</v>
+        <v>0.2289398937012056</v>
       </c>
       <c r="G52">
-        <v>1.774498840675167</v>
+        <v>1.699374665065882</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.136313035946903</v>
       </c>
       <c r="E53">
-        <v>-19.43141654002663</v>
+        <v>-18.70437613155877</v>
       </c>
       <c r="F53">
-        <v>0.9577590722366834</v>
+        <v>-0.09319893536907733</v>
       </c>
       <c r="G53">
-        <v>0.9261974329185007</v>
+        <v>1.635197341527136</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.095166956632097</v>
       </c>
       <c r="E54">
-        <v>-18.7146013378405</v>
+        <v>-18.27213066292724</v>
       </c>
       <c r="F54">
-        <v>0.75581966678222</v>
+        <v>0.09340407598995611</v>
       </c>
       <c r="G54">
-        <v>0.28779466879816</v>
+        <v>1.677039745088908</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.111862351092822</v>
       </c>
       <c r="E55">
-        <v>-17.65500914538229</v>
+        <v>-18.47157617716815</v>
       </c>
       <c r="F55">
-        <v>0.2042330075453076</v>
+        <v>0.07694938590074672</v>
       </c>
       <c r="G55">
-        <v>0.1019200968892585</v>
+        <v>1.262014898928811</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.183989092208041</v>
       </c>
       <c r="E56">
-        <v>-18.0108064531577</v>
+        <v>-17.36175089373615</v>
       </c>
       <c r="F56">
-        <v>0.5652438053593601</v>
+        <v>-0.2623896639212652</v>
       </c>
       <c r="G56">
-        <v>0.5489187320567197</v>
+        <v>1.243230591595751</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.304147917311485</v>
       </c>
       <c r="E57">
-        <v>-17.43508414609864</v>
+        <v>-18.1633622115413</v>
       </c>
       <c r="F57">
-        <v>0.04907316606173776</v>
+        <v>0.1365686446150327</v>
       </c>
       <c r="G57">
-        <v>0.6368851603096908</v>
+        <v>1.019737800873499</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.465744591311853</v>
       </c>
       <c r="E58">
-        <v>-17.62027999228407</v>
+        <v>-17.76467053720306</v>
       </c>
       <c r="F58">
-        <v>0.3883881932290684</v>
+        <v>-0.03839828983687604</v>
       </c>
       <c r="G58">
-        <v>1.194803890175191</v>
+        <v>0.7869011552596512</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.66172778044466</v>
       </c>
       <c r="E59">
-        <v>-15.68103348801586</v>
+        <v>-18.57784024212522</v>
       </c>
       <c r="F59">
-        <v>-0.4731660928287937</v>
+        <v>-0.2699220087149211</v>
       </c>
       <c r="G59">
-        <v>-0.08405368331410532</v>
+        <v>0.9650270372221286</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.882848349574747</v>
       </c>
       <c r="E60">
-        <v>-17.78593913239751</v>
+        <v>-17.58147238566487</v>
       </c>
       <c r="F60">
-        <v>-1.016453339057058</v>
+        <v>-0.2649178412346093</v>
       </c>
       <c r="G60">
-        <v>-0.5336108481808576</v>
+        <v>1.119598781483582</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.12322186339405</v>
       </c>
       <c r="E61">
-        <v>-15.35864045892604</v>
+        <v>-18.42391807721575</v>
       </c>
       <c r="F61">
-        <v>-0.4632853264482013</v>
+        <v>-0.1635190441927274</v>
       </c>
       <c r="G61">
-        <v>-0.7454544965375629</v>
+        <v>-0.1914466620695503</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.373504556740169</v>
       </c>
       <c r="E62">
-        <v>-19.38698548527361</v>
+        <v>-17.69865108998359</v>
       </c>
       <c r="F62">
-        <v>0.0005333213598951294</v>
+        <v>-0.6178934752415066</v>
       </c>
       <c r="G62">
-        <v>-0.07313032794488733</v>
+        <v>0.339255055433594</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.628883132776199</v>
       </c>
       <c r="E63">
-        <v>-16.59453647212322</v>
+        <v>-17.50324249715041</v>
       </c>
       <c r="F63">
-        <v>-0.3019400655679276</v>
+        <v>-0.6517720452812008</v>
       </c>
       <c r="G63">
-        <v>-1.100993527189144</v>
+        <v>0.7113409853036505</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.8855698728765</v>
       </c>
       <c r="E64">
-        <v>-16.85343105326773</v>
+        <v>-16.89259168284954</v>
       </c>
       <c r="F64">
-        <v>-0.2055736004980526</v>
+        <v>-0.5456233895516666</v>
       </c>
       <c r="G64">
-        <v>-1.152226779045151</v>
+        <v>0.472919957009412</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.13739034489014</v>
       </c>
       <c r="E65">
-        <v>-16.13144094977086</v>
+        <v>-16.67359284969133</v>
       </c>
       <c r="F65">
-        <v>-0.6438072927032835</v>
+        <v>-0.713047210433683</v>
       </c>
       <c r="G65">
-        <v>-0.8149055241503586</v>
+        <v>0.05871227390633361</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.38479582527843</v>
       </c>
       <c r="E66">
-        <v>-15.44735305282438</v>
+        <v>-17.73043976946382</v>
       </c>
       <c r="F66">
-        <v>-1.042959439211836</v>
+        <v>-0.7254810051497036</v>
       </c>
       <c r="G66">
-        <v>-0.2914616766105092</v>
+        <v>-0.1164634666681856</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.625352008779021</v>
       </c>
       <c r="E67">
-        <v>-15.72063851120942</v>
+        <v>-17.3035810159206</v>
       </c>
       <c r="F67">
-        <v>-1.148339369991573</v>
+        <v>-0.9546173691728804</v>
       </c>
       <c r="G67">
-        <v>-0.0754251724404759</v>
+        <v>0.07748874900562036</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.856533855014924</v>
       </c>
       <c r="E68">
-        <v>-17.00838321458576</v>
+        <v>-16.96677634353363</v>
       </c>
       <c r="F68">
-        <v>-0.7124656965169177</v>
+        <v>-1.093146078310445</v>
       </c>
       <c r="G68">
-        <v>-1.022446665420909</v>
+        <v>0.01756954989497933</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.079097945002785</v>
       </c>
       <c r="E69">
-        <v>-16.19182864243387</v>
+        <v>-16.67429474240523</v>
       </c>
       <c r="F69">
-        <v>-0.4831255541126522</v>
+        <v>-1.075382567724812</v>
       </c>
       <c r="G69">
-        <v>-0.7486030545144455</v>
+        <v>-0.03656684994634576</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.288100400701123</v>
       </c>
       <c r="E70">
-        <v>-16.85085606224634</v>
+        <v>-16.68315769537241</v>
       </c>
       <c r="F70">
-        <v>-0.7816260909766485</v>
+        <v>-1.075070273213957</v>
       </c>
       <c r="G70">
-        <v>-1.888994567124866</v>
+        <v>-0.5922063997838042</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.483108385263344</v>
       </c>
       <c r="E71">
-        <v>-16.90671675456528</v>
+        <v>-16.70680192744466</v>
       </c>
       <c r="F71">
-        <v>-1.175722711225916</v>
+        <v>-1.111580566492345</v>
       </c>
       <c r="G71">
-        <v>-0.5232096417298622</v>
+        <v>-0.6928271070699012</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.662985045459984</v>
       </c>
       <c r="E72">
-        <v>-16.81562021736649</v>
+        <v>-17.3391615773404</v>
       </c>
       <c r="F72">
-        <v>-0.7077597413016138</v>
+        <v>-1.310325787241613</v>
       </c>
       <c r="G72">
-        <v>-0.4620477281938513</v>
+        <v>-0.214784107969512</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.822768929146658</v>
       </c>
       <c r="E73">
-        <v>-18.2343032141807</v>
+        <v>-16.67818630141659</v>
       </c>
       <c r="F73">
-        <v>-1.395323738075468</v>
+        <v>-1.163025495675805</v>
       </c>
       <c r="G73">
-        <v>-0.7925262215153355</v>
+        <v>-0.1436439286062661</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.961879848849852</v>
       </c>
       <c r="E74">
-        <v>-16.24674240257075</v>
+        <v>-17.04963706267528</v>
       </c>
       <c r="F74">
-        <v>-1.0135068362053</v>
+        <v>-1.519227620716607</v>
       </c>
       <c r="G74">
-        <v>-1.852762653689396</v>
+        <v>-0.3713452396093935</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.078695788022646</v>
       </c>
       <c r="E75">
-        <v>-17.46919031749814</v>
+        <v>-17.468280764218</v>
       </c>
       <c r="F75">
-        <v>-1.404025737641877</v>
+        <v>-1.595581557702248</v>
       </c>
       <c r="G75">
-        <v>-0.799222781391541</v>
+        <v>-0.154473297170204</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.170715981201243</v>
       </c>
       <c r="E76">
-        <v>-18.49319364211389</v>
+        <v>-17.82159445162116</v>
       </c>
       <c r="F76">
-        <v>-1.107893503182484</v>
+        <v>-1.122478568043575</v>
       </c>
       <c r="G76">
-        <v>-0.2795749564871704</v>
+        <v>-0.2100012238785924</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.239597958320095</v>
       </c>
       <c r="E77">
-        <v>-17.92879714233764</v>
+        <v>-18.00570630965081</v>
       </c>
       <c r="F77">
-        <v>-1.241944058140514</v>
+        <v>-1.259055643580143</v>
       </c>
       <c r="G77">
-        <v>-1.493195244133728</v>
+        <v>0.4156349991912042</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.284135160208781</v>
       </c>
       <c r="E78">
-        <v>-19.37261122087838</v>
+        <v>-18.88523602512108</v>
       </c>
       <c r="F78">
-        <v>-1.13398459126846</v>
+        <v>-1.529046259541989</v>
       </c>
       <c r="G78">
-        <v>-0.4253928741346207</v>
+        <v>0.2826515019536668</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.307772091410938</v>
       </c>
       <c r="E79">
-        <v>-18.47388951587608</v>
+        <v>-19.1056261840731</v>
       </c>
       <c r="F79">
-        <v>-1.705582950222203</v>
+        <v>-1.182976724572231</v>
       </c>
       <c r="G79">
-        <v>-0.0635175663604082</v>
+        <v>0.4590490709968271</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.31610069887175</v>
       </c>
       <c r="E80">
-        <v>-19.14490725678333</v>
+        <v>-20.17042650353265</v>
       </c>
       <c r="F80">
-        <v>-1.232132046254354</v>
+        <v>-1.590249356730428</v>
       </c>
       <c r="G80">
-        <v>-0.01851094035420627</v>
+        <v>0.1090134899433133</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.311390464808778</v>
       </c>
       <c r="E81">
-        <v>-20.43141845639619</v>
+        <v>-21.08610161716289</v>
       </c>
       <c r="F81">
-        <v>-1.378946086154719</v>
+        <v>-1.361117134544265</v>
       </c>
       <c r="G81">
-        <v>0.3868176003944958</v>
+        <v>0.6730779125762942</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.299620004463424</v>
       </c>
       <c r="E82">
-        <v>-21.79113415882049</v>
+        <v>-22.03601995816635</v>
       </c>
       <c r="F82">
-        <v>-1.344095012784138</v>
+        <v>-1.508018153021924</v>
       </c>
       <c r="G82">
-        <v>0.6111614938534515</v>
+        <v>0.3277312288084199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.28755613748395</v>
       </c>
       <c r="E83">
-        <v>-22.98148190341827</v>
+        <v>-23.54792178316633</v>
       </c>
       <c r="F83">
-        <v>-1.758071622333191</v>
+        <v>-1.200859520063867</v>
       </c>
       <c r="G83">
-        <v>0.9326955762057816</v>
+        <v>0.8871694120259481</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.278951688896384</v>
       </c>
       <c r="E84">
-        <v>-22.73400450020571</v>
+        <v>-23.41880259628874</v>
       </c>
       <c r="F84">
-        <v>-1.345507379205911</v>
+        <v>-1.33538721464591</v>
       </c>
       <c r="G84">
-        <v>0.4965158666238939</v>
+        <v>1.212804974130917</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.281912957820897</v>
       </c>
       <c r="E85">
-        <v>-22.81473462193773</v>
+        <v>-24.7413096784539</v>
       </c>
       <c r="F85">
-        <v>-1.589137687675871</v>
+        <v>-1.562131253609802</v>
       </c>
       <c r="G85">
-        <v>0.9747990542266656</v>
+        <v>1.257067537928652</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.299006096695065</v>
       </c>
       <c r="E86">
-        <v>-24.80076705178014</v>
+        <v>-25.49991864620177</v>
       </c>
       <c r="F86">
-        <v>-1.648608668625056</v>
+        <v>-1.166330681612975</v>
       </c>
       <c r="G86">
-        <v>1.544635833150598</v>
+        <v>1.972787503114812</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.33740789428109</v>
       </c>
       <c r="E87">
-        <v>-24.96482305232219</v>
+        <v>-27.16679755178774</v>
       </c>
       <c r="F87">
-        <v>-1.621050541868722</v>
+        <v>-1.243102115769628</v>
       </c>
       <c r="G87">
-        <v>1.220206435046723</v>
+        <v>1.870417596952669</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.405498124461136</v>
       </c>
       <c r="E88">
-        <v>-26.56390078303033</v>
+        <v>-28.51143917370856</v>
       </c>
       <c r="F88">
-        <v>-1.309309380438378</v>
+        <v>-1.228955257264618</v>
       </c>
       <c r="G88">
-        <v>0.100387589814275</v>
+        <v>1.665200018368209</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.506042543009907</v>
       </c>
       <c r="E89">
-        <v>-29.26076156093413</v>
+        <v>-30.49771041320215</v>
       </c>
       <c r="F89">
-        <v>-1.512953566007803</v>
+        <v>-1.030347545504214</v>
       </c>
       <c r="G89">
-        <v>1.445558075917849</v>
+        <v>2.13878908719616</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.648188175867159</v>
       </c>
       <c r="E90">
-        <v>-31.45787057333264</v>
+        <v>-31.29436694989679</v>
       </c>
       <c r="F90">
-        <v>-1.371059200112665</v>
+        <v>-1.128077503319097</v>
       </c>
       <c r="G90">
-        <v>1.88221555175991</v>
+        <v>1.788615136679317</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.838730155558699</v>
       </c>
       <c r="E91">
-        <v>-33.26959480047766</v>
+        <v>-33.22870643498472</v>
       </c>
       <c r="F91">
-        <v>-1.583185039519354</v>
+        <v>-1.297018893283042</v>
       </c>
       <c r="G91">
-        <v>1.644368887275717</v>
+        <v>2.086083375390765</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.081859697099306</v>
       </c>
       <c r="E92">
-        <v>-35.77840855262153</v>
+        <v>-35.04522554460425</v>
       </c>
       <c r="F92">
-        <v>-0.9053021725820174</v>
+        <v>-0.9570229481106102</v>
       </c>
       <c r="G92">
-        <v>1.268969922519537</v>
+        <v>1.862603638391467</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.388396428145816</v>
       </c>
       <c r="E93">
-        <v>-37.40228510815022</v>
+        <v>-36.95480566037921</v>
       </c>
       <c r="F93">
-        <v>-1.251110771819893</v>
+        <v>-0.8922404753746749</v>
       </c>
       <c r="G93">
-        <v>1.165532221819629</v>
+        <v>2.091827013491214</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.756013754865002</v>
       </c>
       <c r="E94">
-        <v>-36.4919510242837</v>
+        <v>-38.93775848402426</v>
       </c>
       <c r="F94">
-        <v>-1.530871152930356</v>
+        <v>-1.191143598796432</v>
       </c>
       <c r="G94">
-        <v>1.856397898498391</v>
+        <v>1.380252910715741</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.190443351281806</v>
       </c>
       <c r="E95">
-        <v>-41.31948396962839</v>
+        <v>-41.2660238334552</v>
       </c>
       <c r="F95">
-        <v>-1.669064373269787</v>
+        <v>-1.237552054170871</v>
       </c>
       <c r="G95">
-        <v>1.258555662345586</v>
+        <v>1.479623071342695</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.697988496616561</v>
       </c>
       <c r="E96">
-        <v>-42.56286199302725</v>
+        <v>-43.04557313246677</v>
       </c>
       <c r="F96">
-        <v>-1.831060730928661</v>
+        <v>-1.531137058866655</v>
       </c>
       <c r="G96">
-        <v>0.7780794492862795</v>
+        <v>1.386395992738631</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.261877324127596</v>
       </c>
       <c r="E97">
-        <v>-44.72077299694202</v>
+        <v>-45.84827642437816</v>
       </c>
       <c r="F97">
-        <v>-1.634074134175536</v>
+        <v>-1.459098087682196</v>
       </c>
       <c r="G97">
-        <v>1.112523663641665</v>
+        <v>1.655336625302984</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.893237837802323</v>
       </c>
       <c r="E98">
-        <v>-46.48139299703786</v>
+        <v>-47.44221455607182</v>
       </c>
       <c r="F98">
-        <v>-1.56414004456159</v>
+        <v>-1.565763644671077</v>
       </c>
       <c r="G98">
-        <v>0.238937194520066</v>
+        <v>1.197863682835976</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.558289907403219</v>
       </c>
       <c r="E99">
-        <v>-50.2239129817079</v>
+        <v>-49.2914806986848</v>
       </c>
       <c r="F99">
-        <v>-1.882801387274921</v>
+        <v>-1.480096372975761</v>
       </c>
       <c r="G99">
-        <v>-0.2522770110424899</v>
+        <v>1.153548904146419</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.27587328922629</v>
       </c>
       <c r="E100">
-        <v>-50.3322578055387</v>
+        <v>-51.77743932890814</v>
       </c>
       <c r="F100">
-        <v>-2.148633598874713</v>
+        <v>-1.86228355507498</v>
       </c>
       <c r="G100">
-        <v>0.9262026544076829</v>
+        <v>0.985617979812239</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.97866651083055</v>
       </c>
       <c r="E101">
-        <v>-53.4150993545211</v>
+        <v>-53.30513477827362</v>
       </c>
       <c r="F101">
-        <v>-2.211825606197273</v>
+        <v>-1.922003874612408</v>
       </c>
       <c r="G101">
-        <v>-1.273130361059607</v>
+        <v>0.5874846511566452</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.73363167701207</v>
       </c>
       <c r="E102">
-        <v>-53.34044538095731</v>
+        <v>-55.02116590158609</v>
       </c>
       <c r="F102">
-        <v>-1.980255498744671</v>
+        <v>-2.311149342895142</v>
       </c>
       <c r="G102">
-        <v>-0.2189221381464265</v>
+        <v>-0.1010104694333861</v>
       </c>
     </row>
   </sheetData>
